--- a/matlab/results/group_statistics.xlsx
+++ b/matlab/results/group_statistics.xlsx
@@ -19,22 +19,22 @@
     <t>Feature</t>
   </si>
   <si>
-    <t>Sehir</t>
-  </si>
-  <si>
-    <t>Bolge</t>
-  </si>
-  <si>
-    <t>Urun</t>
-  </si>
-  <si>
-    <t>Kategori</t>
-  </si>
-  <si>
-    <t>Satis_Kanali</t>
-  </si>
-  <si>
-    <t>Musteri_Tipi</t>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Sales_Channel</t>
+  </si>
+  <si>
+    <t>Customer_Type</t>
   </si>
   <si>
     <t>Group</t>
@@ -55,6 +55,12 @@
     <t>Gaziantep</t>
   </si>
   <si>
+    <t>Istanbul</t>
+  </si>
+  <si>
+    <t>Izmir</t>
+  </si>
+  <si>
     <t>Konya</t>
   </si>
   <si>
@@ -64,28 +70,22 @@
     <t>Trabzon</t>
   </si>
   <si>
-    <t>İstanbul</t>
-  </si>
-  <si>
-    <t>İzmir</t>
-  </si>
-  <si>
-    <t>Akdeniz</t>
-  </si>
-  <si>
-    <t>Ege</t>
-  </si>
-  <si>
-    <t>Güneydoğu Anadolu</t>
-  </si>
-  <si>
-    <t>Karadeniz</t>
+    <t>Aegean</t>
+  </si>
+  <si>
+    <t>Black Sea</t>
+  </si>
+  <si>
+    <t>Central Anatolia</t>
   </si>
   <si>
     <t>Marmara</t>
   </si>
   <si>
-    <t>İç Anadolu</t>
+    <t>Mediterranean</t>
+  </si>
+  <si>
+    <t>Southeastern Anatolia</t>
   </si>
   <si>
     <t>Backpack</t>
@@ -124,37 +124,37 @@
     <t>Wireless Mouse</t>
   </si>
   <si>
-    <t>Aksesuar</t>
-  </si>
-  <si>
-    <t>Elektronik</t>
-  </si>
-  <si>
-    <t>Kırtasiye</t>
-  </si>
-  <si>
-    <t>Mobilya</t>
-  </si>
-  <si>
-    <t>Ofis Aksesuarları</t>
-  </si>
-  <si>
-    <t>Bayi</t>
-  </si>
-  <si>
-    <t>Mağaza</t>
+    <t>Accessories</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>Furniture</t>
+  </si>
+  <si>
+    <t>Office Accessories</t>
+  </si>
+  <si>
+    <t>Stationery</t>
+  </si>
+  <si>
+    <t>Dealer</t>
   </si>
   <si>
     <t>Online</t>
   </si>
   <si>
-    <t>Bireysel</t>
-  </si>
-  <si>
-    <t>KOBI</t>
-  </si>
-  <si>
-    <t>Kurumsal</t>
+    <t>Store</t>
+  </si>
+  <si>
+    <t>Corporate</t>
+  </si>
+  <si>
+    <t>Individual</t>
+  </si>
+  <si>
+    <t>SME</t>
   </si>
   <si>
     <t>N</t>
@@ -269,8 +269,8 @@
   <dimension ref="A1:T40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="true"/>
-    <col min="2" max="2" width="20" customWidth="true"/>
+    <col min="1" max="1" width="15" customWidth="true"/>
+    <col min="2" max="2" width="20.85546875" customWidth="true"/>
     <col min="3" max="3" width="4.140625" customWidth="true"/>
     <col min="4" max="4" width="11.7109375" customWidth="true"/>
     <col min="5" max="5" width="8.7109375" customWidth="true"/>
@@ -671,58 +671,58 @@
         <v>13</v>
       </c>
       <c r="C7" s="0">
-        <v>59</v>
+        <v>291</v>
       </c>
       <c r="D7" s="0">
-        <v>1562.4249152542375</v>
+        <v>1385.1108247422683</v>
       </c>
       <c r="E7" s="0">
-        <v>853.75999999999999</v>
+        <v>702.22000000000003</v>
       </c>
       <c r="F7" s="0">
-        <v>1892.6291857154627</v>
+        <v>2031.8378826731046</v>
       </c>
       <c r="G7" s="0">
-        <v>3582045.2346219756</v>
+        <v>4128365.1814655247</v>
       </c>
       <c r="H7" s="0">
-        <v>-1627.0699999999999</v>
+        <v>-32.960000000000001</v>
       </c>
       <c r="I7" s="0">
-        <v>8441.75</v>
+        <v>14240.790000000001</v>
       </c>
       <c r="J7" s="0">
-        <v>319.61500000000001</v>
+        <v>307.67000000000002</v>
       </c>
       <c r="K7" s="0">
-        <v>2305.8649999999998</v>
+        <v>1535.6774999999998</v>
       </c>
       <c r="L7" s="0">
-        <v>1986.2499999999998</v>
+        <v>1228.0074999999997</v>
       </c>
       <c r="M7" s="0">
-        <v>246.39933257881955</v>
+        <v>119.10844608773466</v>
       </c>
       <c r="N7" s="0">
-        <v>1.2113408889204089</v>
+        <v>1.4669135829266042</v>
       </c>
       <c r="O7" s="0">
-        <v>-330.20427046122518</v>
+        <v>-646.72705793083628</v>
       </c>
       <c r="P7" s="0">
-        <v>3455.0541009696999</v>
+        <v>3416.9487074153731</v>
       </c>
       <c r="Q7" s="0">
-        <v>1069.203063149497</v>
+        <v>1150.6842138775676</v>
       </c>
       <c r="R7" s="0">
-        <v>2055.6467673589782</v>
+        <v>1619.537435606969</v>
       </c>
       <c r="S7" s="0">
-        <v>1.6221744489019356</v>
+        <v>3.3858252144697265</v>
       </c>
       <c r="T7" s="0">
-        <v>2.8230384607305545</v>
+        <v>14.047372688524106</v>
       </c>
     </row>
     <row r="8">
@@ -733,58 +733,58 @@
         <v>14</v>
       </c>
       <c r="C8" s="0">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="D8" s="0">
-        <v>1667.955641025641</v>
+        <v>1497.2519327731095</v>
       </c>
       <c r="E8" s="0">
-        <v>867.80999999999995</v>
+        <v>815.38</v>
       </c>
       <c r="F8" s="0">
-        <v>2191.2309171244542</v>
+        <v>2520.8596507555212</v>
       </c>
       <c r="G8" s="0">
-        <v>4801492.9321620772</v>
+        <v>6354733.3788072495</v>
       </c>
       <c r="H8" s="0">
-        <v>74.870000000000005</v>
+        <v>-6485.9099999999999</v>
       </c>
       <c r="I8" s="0">
-        <v>10522.15</v>
+        <v>18397.919999999998</v>
       </c>
       <c r="J8" s="0">
-        <v>382.92249999999996</v>
+        <v>292.67000000000002</v>
       </c>
       <c r="K8" s="0">
-        <v>1615.4950000000001</v>
+        <v>2048.4975</v>
       </c>
       <c r="L8" s="0">
-        <v>1232.5725000000002</v>
+        <v>1755.8274999999999</v>
       </c>
       <c r="M8" s="0">
-        <v>350.87776131976676</v>
+        <v>231.08682530666479</v>
       </c>
       <c r="N8" s="0">
-        <v>1.3137225374753052</v>
+        <v>1.683657636752256</v>
       </c>
       <c r="O8" s="0">
-        <v>-523.27527609881326</v>
+        <v>-1023.6077179824117</v>
       </c>
       <c r="P8" s="0">
-        <v>3859.1865581500952</v>
+        <v>4018.111583528631</v>
       </c>
       <c r="Q8" s="0">
-        <v>957.64074876340817</v>
+        <v>1039.6371054457313</v>
       </c>
       <c r="R8" s="0">
-        <v>2378.2705332878736</v>
+        <v>1954.8667601004877</v>
       </c>
       <c r="S8" s="0">
-        <v>2.4691622355600349</v>
+        <v>3.312663798463789</v>
       </c>
       <c r="T8" s="0">
-        <v>6.6462098109578633</v>
+        <v>19.310847913970036</v>
       </c>
     </row>
     <row r="9">
@@ -795,58 +795,58 @@
         <v>15</v>
       </c>
       <c r="C9" s="0">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="D9" s="0">
-        <v>1780.6703333333337</v>
+        <v>1562.4249152542375</v>
       </c>
       <c r="E9" s="0">
-        <v>1031.7550000000001</v>
+        <v>853.75999999999999</v>
       </c>
       <c r="F9" s="0">
-        <v>2184.5041084664463</v>
+        <v>1892.6291857154627</v>
       </c>
       <c r="G9" s="0">
-        <v>4772058.1999067841</v>
+        <v>3582045.2346219756</v>
       </c>
       <c r="H9" s="0">
-        <v>-800.01999999999998</v>
+        <v>-1627.0699999999999</v>
       </c>
       <c r="I9" s="0">
-        <v>9088.1200000000008</v>
+        <v>8441.75</v>
       </c>
       <c r="J9" s="0">
-        <v>403.67000000000002</v>
+        <v>319.61500000000001</v>
       </c>
       <c r="K9" s="0">
-        <v>2416.1199999999999</v>
+        <v>2305.8649999999998</v>
       </c>
       <c r="L9" s="0">
-        <v>2012.4499999999998</v>
+        <v>1986.2499999999998</v>
       </c>
       <c r="M9" s="0">
-        <v>398.83405905659493</v>
+        <v>246.39933257881955</v>
       </c>
       <c r="N9" s="0">
-        <v>1.2267875010739098</v>
+        <v>1.2113408889204089</v>
       </c>
       <c r="O9" s="0">
-        <v>-403.83377513311257</v>
+        <v>-330.20427046122518</v>
       </c>
       <c r="P9" s="0">
-        <v>3965.1744417997798</v>
+        <v>3455.0541009696999</v>
       </c>
       <c r="Q9" s="0">
-        <v>964.96309345868008</v>
+        <v>1069.203063149497</v>
       </c>
       <c r="R9" s="0">
-        <v>2596.3775732079876</v>
+        <v>2055.6467673589782</v>
       </c>
       <c r="S9" s="0">
-        <v>1.8392616520859229</v>
+        <v>1.6221744489019356</v>
       </c>
       <c r="T9" s="0">
-        <v>3.4405994630397547</v>
+        <v>2.8230384607305545</v>
       </c>
     </row>
     <row r="10">
@@ -857,58 +857,58 @@
         <v>16</v>
       </c>
       <c r="C10" s="0">
-        <v>291</v>
+        <v>39</v>
       </c>
       <c r="D10" s="0">
-        <v>1385.1108247422683</v>
+        <v>1667.955641025641</v>
       </c>
       <c r="E10" s="0">
-        <v>702.22000000000003</v>
+        <v>867.80999999999995</v>
       </c>
       <c r="F10" s="0">
-        <v>2031.8378826731046</v>
+        <v>2191.2309171244542</v>
       </c>
       <c r="G10" s="0">
-        <v>4128365.1814655247</v>
+        <v>4801492.9321620772</v>
       </c>
       <c r="H10" s="0">
-        <v>-32.960000000000001</v>
+        <v>74.870000000000005</v>
       </c>
       <c r="I10" s="0">
-        <v>14240.790000000001</v>
+        <v>10522.15</v>
       </c>
       <c r="J10" s="0">
-        <v>307.67000000000002</v>
+        <v>382.92249999999996</v>
       </c>
       <c r="K10" s="0">
-        <v>1535.6774999999998</v>
+        <v>1615.4950000000001</v>
       </c>
       <c r="L10" s="0">
-        <v>1228.0074999999997</v>
+        <v>1232.5725000000002</v>
       </c>
       <c r="M10" s="0">
-        <v>119.10844608773466</v>
+        <v>350.87776131976676</v>
       </c>
       <c r="N10" s="0">
-        <v>1.4669135829266042</v>
+        <v>1.3137225374753052</v>
       </c>
       <c r="O10" s="0">
-        <v>-646.72705793083628</v>
+        <v>-523.27527609881326</v>
       </c>
       <c r="P10" s="0">
-        <v>3416.9487074153731</v>
+        <v>3859.1865581500952</v>
       </c>
       <c r="Q10" s="0">
-        <v>1150.6842138775676</v>
+        <v>957.64074876340817</v>
       </c>
       <c r="R10" s="0">
-        <v>1619.537435606969</v>
+        <v>2378.2705332878736</v>
       </c>
       <c r="S10" s="0">
-        <v>3.3858252144697265</v>
+        <v>2.4691622355600349</v>
       </c>
       <c r="T10" s="0">
-        <v>14.047372688524106</v>
+        <v>6.6462098109578633</v>
       </c>
     </row>
     <row r="11">
@@ -919,58 +919,58 @@
         <v>17</v>
       </c>
       <c r="C11" s="0">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="D11" s="0">
-        <v>1497.2519327731095</v>
+        <v>1780.6703333333337</v>
       </c>
       <c r="E11" s="0">
-        <v>815.38</v>
+        <v>1031.7550000000001</v>
       </c>
       <c r="F11" s="0">
-        <v>2520.8596507555212</v>
+        <v>2184.5041084664463</v>
       </c>
       <c r="G11" s="0">
-        <v>6354733.3788072495</v>
+        <v>4772058.1999067841</v>
       </c>
       <c r="H11" s="0">
-        <v>-6485.9099999999999</v>
+        <v>-800.01999999999998</v>
       </c>
       <c r="I11" s="0">
-        <v>18397.919999999998</v>
+        <v>9088.1200000000008</v>
       </c>
       <c r="J11" s="0">
-        <v>292.67000000000002</v>
+        <v>403.67000000000002</v>
       </c>
       <c r="K11" s="0">
-        <v>2048.4975</v>
+        <v>2416.1199999999999</v>
       </c>
       <c r="L11" s="0">
-        <v>1755.8274999999999</v>
+        <v>2012.4499999999998</v>
       </c>
       <c r="M11" s="0">
-        <v>231.08682530666479</v>
+        <v>398.83405905659493</v>
       </c>
       <c r="N11" s="0">
-        <v>1.683657636752256</v>
+        <v>1.2267875010739098</v>
       </c>
       <c r="O11" s="0">
-        <v>-1023.6077179824117</v>
+        <v>-403.83377513311257</v>
       </c>
       <c r="P11" s="0">
-        <v>4018.111583528631</v>
+        <v>3965.1744417997798</v>
       </c>
       <c r="Q11" s="0">
-        <v>1039.6371054457313</v>
+        <v>964.96309345868008</v>
       </c>
       <c r="R11" s="0">
-        <v>1954.8667601004877</v>
+        <v>2596.3775732079876</v>
       </c>
       <c r="S11" s="0">
-        <v>3.312663798463789</v>
+        <v>1.8392616520859229</v>
       </c>
       <c r="T11" s="0">
-        <v>19.310847913970036</v>
+        <v>3.4405994630397547</v>
       </c>
     </row>
     <row r="12">
@@ -981,58 +981,58 @@
         <v>18</v>
       </c>
       <c r="C12" s="0">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D12" s="0">
-        <v>1662.42176</v>
+        <v>1497.2519327731095</v>
       </c>
       <c r="E12" s="0">
-        <v>848.62</v>
+        <v>815.38</v>
       </c>
       <c r="F12" s="0">
-        <v>2129.2436343426775</v>
+        <v>2520.8596507555212</v>
       </c>
       <c r="G12" s="0">
-        <v>4533678.4543888131</v>
+        <v>6354733.3788072495</v>
       </c>
       <c r="H12" s="0">
-        <v>-279.55000000000001</v>
+        <v>-6485.9099999999999</v>
       </c>
       <c r="I12" s="0">
-        <v>13620.639999999999</v>
+        <v>18397.919999999998</v>
       </c>
       <c r="J12" s="0">
-        <v>354.51999999999998</v>
+        <v>292.67000000000002</v>
       </c>
       <c r="K12" s="0">
-        <v>2029.9175</v>
+        <v>2048.4975</v>
       </c>
       <c r="L12" s="0">
-        <v>1675.3975</v>
+        <v>1755.8274999999999</v>
       </c>
       <c r="M12" s="0">
-        <v>190.4453402819573</v>
+        <v>231.08682530666479</v>
       </c>
       <c r="N12" s="0">
-        <v>1.2808083276909692</v>
+        <v>1.683657636752256</v>
       </c>
       <c r="O12" s="0">
-        <v>-466.82187434267757</v>
+        <v>-1023.6077179824117</v>
       </c>
       <c r="P12" s="0">
-        <v>3791.6653943426772</v>
+        <v>4018.111583528631</v>
       </c>
       <c r="Q12" s="0">
-        <v>1285.4770846798751</v>
+        <v>1039.6371054457313</v>
       </c>
       <c r="R12" s="0">
-        <v>2039.3664353201248</v>
+        <v>1954.8667601004877</v>
       </c>
       <c r="S12" s="0">
-        <v>2.6864067115596635</v>
+        <v>3.312663798463789</v>
       </c>
       <c r="T12" s="0">
-        <v>9.7038529522023218</v>
+        <v>19.310847913970036</v>
       </c>
     </row>
     <row r="13">
@@ -1043,58 +1043,58 @@
         <v>19</v>
       </c>
       <c r="C13" s="0">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="D13" s="0">
-        <v>1497.2519327731095</v>
+        <v>1716.9620289855072</v>
       </c>
       <c r="E13" s="0">
-        <v>815.38</v>
+        <v>932.52999999999997</v>
       </c>
       <c r="F13" s="0">
-        <v>2520.8596507555212</v>
+        <v>2172.9007620511097</v>
       </c>
       <c r="G13" s="0">
-        <v>6354733.3788072495</v>
+        <v>4721497.7217222937</v>
       </c>
       <c r="H13" s="0">
-        <v>-6485.9099999999999</v>
+        <v>-800.01999999999998</v>
       </c>
       <c r="I13" s="0">
-        <v>18397.919999999998</v>
+        <v>10522.15</v>
       </c>
       <c r="J13" s="0">
-        <v>292.67000000000002</v>
+        <v>392.91499999999996</v>
       </c>
       <c r="K13" s="0">
-        <v>2048.4975</v>
+        <v>1660.6475000000003</v>
       </c>
       <c r="L13" s="0">
-        <v>1755.8274999999999</v>
+        <v>1267.7325000000003</v>
       </c>
       <c r="M13" s="0">
-        <v>231.08682530666479</v>
+        <v>261.58651191024086</v>
       </c>
       <c r="N13" s="0">
-        <v>1.683657636752256</v>
+        <v>1.2655496891419322</v>
       </c>
       <c r="O13" s="0">
-        <v>-1023.6077179824117</v>
+        <v>-455.93873306560249</v>
       </c>
       <c r="P13" s="0">
-        <v>4018.111583528631</v>
+        <v>3889.8627910366167</v>
       </c>
       <c r="Q13" s="0">
-        <v>1039.6371054457313</v>
+        <v>1194.9742715875154</v>
       </c>
       <c r="R13" s="0">
-        <v>1954.8667601004877</v>
+        <v>2238.949786383499</v>
       </c>
       <c r="S13" s="0">
-        <v>3.312663798463789</v>
+        <v>2.1480949773361382</v>
       </c>
       <c r="T13" s="0">
-        <v>19.310847913970036</v>
+        <v>4.7872226605841988</v>
       </c>
     </row>
     <row r="14">
@@ -1105,58 +1105,58 @@
         <v>20</v>
       </c>
       <c r="C14" s="0">
-        <v>46</v>
+        <v>221</v>
       </c>
       <c r="D14" s="0">
-        <v>1138.8852173913044</v>
+        <v>1221.792036199095</v>
       </c>
       <c r="E14" s="0">
-        <v>765.6099999999999</v>
+        <v>685.40999999999997</v>
       </c>
       <c r="F14" s="0">
-        <v>1715.1878538978872</v>
+        <v>1551.9937338981163</v>
       </c>
       <c r="G14" s="0">
-        <v>2941869.3741588402</v>
+        <v>2408684.5500590168</v>
       </c>
       <c r="H14" s="0">
-        <v>-3409.6799999999998</v>
+        <v>-1627.0699999999999</v>
       </c>
       <c r="I14" s="0">
-        <v>6635.1499999999996</v>
+        <v>9133.9300000000003</v>
       </c>
       <c r="J14" s="0">
-        <v>326.60000000000002</v>
+        <v>266.20749999999998</v>
       </c>
       <c r="K14" s="0">
-        <v>1783.0999999999999</v>
+        <v>1631.1524999999999</v>
       </c>
       <c r="L14" s="0">
-        <v>1456.5</v>
+        <v>1364.9449999999999</v>
       </c>
       <c r="M14" s="0">
-        <v>252.8906523518244</v>
+        <v>104.39839612460153</v>
       </c>
       <c r="N14" s="0">
-        <v>1.5060234584716481</v>
+        <v>1.2702601489581273</v>
       </c>
       <c r="O14" s="0">
-        <v>-576.30263650658276</v>
+        <v>-330.20169769902123</v>
       </c>
       <c r="P14" s="0">
-        <v>2854.0730712891918</v>
+        <v>2773.7857700972113</v>
       </c>
       <c r="Q14" s="0">
-        <v>629.53729747320585</v>
+        <v>1016.0430932807161</v>
       </c>
       <c r="R14" s="0">
-        <v>1648.233137309403</v>
+        <v>1427.5409791174739</v>
       </c>
       <c r="S14" s="0">
-        <v>0.79314368566654381</v>
+        <v>2.3542593248670949</v>
       </c>
       <c r="T14" s="0">
-        <v>3.2597766648654467</v>
+        <v>7.0005946256932816</v>
       </c>
     </row>
     <row r="15">
@@ -1167,58 +1167,58 @@
         <v>21</v>
       </c>
       <c r="C15" s="0">
-        <v>69</v>
+        <v>378</v>
       </c>
       <c r="D15" s="0">
-        <v>1716.9620289855072</v>
+        <v>1379.686613756614</v>
       </c>
       <c r="E15" s="0">
-        <v>932.52999999999997</v>
+        <v>724.37</v>
       </c>
       <c r="F15" s="0">
-        <v>2172.9007620511097</v>
+        <v>1924.1664962837451</v>
       </c>
       <c r="G15" s="0">
-        <v>4721497.7217222937</v>
+        <v>3702416.7054208634</v>
       </c>
       <c r="H15" s="0">
-        <v>-800.01999999999998</v>
+        <v>-32.960000000000001</v>
       </c>
       <c r="I15" s="0">
-        <v>10522.15</v>
+        <v>14240.790000000001</v>
       </c>
       <c r="J15" s="0">
-        <v>392.91499999999996</v>
+        <v>297.43000000000001</v>
       </c>
       <c r="K15" s="0">
-        <v>1660.6475000000003</v>
+        <v>1618.53</v>
       </c>
       <c r="L15" s="0">
-        <v>1267.7325000000003</v>
+        <v>1321.0999999999999</v>
       </c>
       <c r="M15" s="0">
-        <v>261.58651191024086</v>
+        <v>98.968445420467646</v>
       </c>
       <c r="N15" s="0">
-        <v>1.2655496891419322</v>
+        <v>1.3946402589531692</v>
       </c>
       <c r="O15" s="0">
-        <v>-455.93873306560249</v>
+        <v>-544.47988252713117</v>
       </c>
       <c r="P15" s="0">
-        <v>3889.8627910366167</v>
+        <v>3303.8531100403589</v>
       </c>
       <c r="Q15" s="0">
-        <v>1194.9742715875154</v>
+        <v>1185.0872964028961</v>
       </c>
       <c r="R15" s="0">
-        <v>2238.949786383499</v>
+        <v>1574.2859311103318</v>
       </c>
       <c r="S15" s="0">
-        <v>2.1480949773361382</v>
+        <v>3.2565127494880763</v>
       </c>
       <c r="T15" s="0">
-        <v>4.7872226605841988</v>
+        <v>13.734780224354026</v>
       </c>
     </row>
     <row r="16">
@@ -1229,58 +1229,58 @@
         <v>22</v>
       </c>
       <c r="C16" s="0">
-        <v>378</v>
+        <v>125</v>
       </c>
       <c r="D16" s="0">
-        <v>1379.686613756614</v>
+        <v>1662.42176</v>
       </c>
       <c r="E16" s="0">
-        <v>724.37</v>
+        <v>848.62</v>
       </c>
       <c r="F16" s="0">
-        <v>1924.1664962837451</v>
+        <v>2129.2436343426775</v>
       </c>
       <c r="G16" s="0">
-        <v>3702416.7054208634</v>
+        <v>4533678.4543888131</v>
       </c>
       <c r="H16" s="0">
-        <v>-32.960000000000001</v>
+        <v>-279.55000000000001</v>
       </c>
       <c r="I16" s="0">
-        <v>14240.790000000001</v>
+        <v>13620.639999999999</v>
       </c>
       <c r="J16" s="0">
-        <v>297.43000000000001</v>
+        <v>354.51999999999998</v>
       </c>
       <c r="K16" s="0">
-        <v>1618.53</v>
+        <v>2029.9175</v>
       </c>
       <c r="L16" s="0">
-        <v>1321.0999999999999</v>
+        <v>1675.3975</v>
       </c>
       <c r="M16" s="0">
-        <v>98.968445420467646</v>
+        <v>190.4453402819573</v>
       </c>
       <c r="N16" s="0">
-        <v>1.3946402589531692</v>
+        <v>1.2808083276909692</v>
       </c>
       <c r="O16" s="0">
-        <v>-544.47988252713117</v>
+        <v>-466.82187434267757</v>
       </c>
       <c r="P16" s="0">
-        <v>3303.8531100403589</v>
+        <v>3791.6653943426772</v>
       </c>
       <c r="Q16" s="0">
-        <v>1185.0872964028961</v>
+        <v>1285.4770846798751</v>
       </c>
       <c r="R16" s="0">
-        <v>1574.2859311103318</v>
+        <v>2039.3664353201248</v>
       </c>
       <c r="S16" s="0">
-        <v>3.2565127494880763</v>
+        <v>2.6864067115596635</v>
       </c>
       <c r="T16" s="0">
-        <v>13.734780224354026</v>
+        <v>9.7038529522023218</v>
       </c>
     </row>
     <row r="17">
@@ -1291,58 +1291,58 @@
         <v>23</v>
       </c>
       <c r="C17" s="0">
-        <v>221</v>
+        <v>46</v>
       </c>
       <c r="D17" s="0">
-        <v>1221.792036199095</v>
+        <v>1138.8852173913044</v>
       </c>
       <c r="E17" s="0">
-        <v>685.40999999999997</v>
+        <v>765.6099999999999</v>
       </c>
       <c r="F17" s="0">
-        <v>1551.9937338981163</v>
+        <v>1715.1878538978872</v>
       </c>
       <c r="G17" s="0">
-        <v>2408684.5500590168</v>
+        <v>2941869.3741588402</v>
       </c>
       <c r="H17" s="0">
-        <v>-1627.0699999999999</v>
+        <v>-3409.6799999999998</v>
       </c>
       <c r="I17" s="0">
-        <v>9133.9300000000003</v>
+        <v>6635.1499999999996</v>
       </c>
       <c r="J17" s="0">
-        <v>266.20749999999998</v>
+        <v>326.60000000000002</v>
       </c>
       <c r="K17" s="0">
-        <v>1631.1524999999999</v>
+        <v>1783.0999999999999</v>
       </c>
       <c r="L17" s="0">
-        <v>1364.9449999999999</v>
+        <v>1456.5</v>
       </c>
       <c r="M17" s="0">
-        <v>104.39839612460153</v>
+        <v>252.8906523518244</v>
       </c>
       <c r="N17" s="0">
-        <v>1.2702601489581273</v>
+        <v>1.5060234584716481</v>
       </c>
       <c r="O17" s="0">
-        <v>-330.20169769902123</v>
+        <v>-576.30263650658276</v>
       </c>
       <c r="P17" s="0">
-        <v>2773.7857700972113</v>
+        <v>2854.0730712891918</v>
       </c>
       <c r="Q17" s="0">
-        <v>1016.0430932807161</v>
+        <v>629.53729747320585</v>
       </c>
       <c r="R17" s="0">
-        <v>1427.5409791174739</v>
+        <v>1648.233137309403</v>
       </c>
       <c r="S17" s="0">
-        <v>2.3542593248670949</v>
+        <v>0.79314368566654381</v>
       </c>
       <c r="T17" s="0">
-        <v>7.0005946256932816</v>
+        <v>3.2597766648654467</v>
       </c>
     </row>
     <row r="18">
@@ -2221,58 +2221,58 @@
         <v>38</v>
       </c>
       <c r="C32" s="0">
-        <v>164</v>
+        <v>85</v>
       </c>
       <c r="D32" s="0">
-        <v>247.55975609756095</v>
+        <v>3955.5442352941177</v>
       </c>
       <c r="E32" s="0">
-        <v>162.56999999999999</v>
+        <v>3029.2600000000002</v>
       </c>
       <c r="F32" s="0">
-        <v>257.037318037175</v>
+        <v>3633.209196544517</v>
       </c>
       <c r="G32" s="0">
-        <v>66068.182863743845</v>
+        <v>13200209.065855656</v>
       </c>
       <c r="H32" s="0">
-        <v>24.920000000000002</v>
+        <v>-1094.49</v>
       </c>
       <c r="I32" s="0">
-        <v>1378.8599999999999</v>
+        <v>18397.919999999998</v>
       </c>
       <c r="J32" s="0">
-        <v>79.549999999999997</v>
+        <v>1255.01</v>
       </c>
       <c r="K32" s="0">
-        <v>346.89499999999998</v>
+        <v>5424.0675000000001</v>
       </c>
       <c r="L32" s="0">
-        <v>267.34499999999997</v>
+        <v>4169.0574999999999</v>
       </c>
       <c r="M32" s="0">
-        <v>20.071242451811838</v>
+        <v>394.07686717867705</v>
       </c>
       <c r="N32" s="0">
-        <v>1.0382839363271914</v>
+        <v>0.91851057159884519</v>
       </c>
       <c r="O32" s="0">
-        <v>-9.4775619396140485</v>
+        <v>322.3350387496007</v>
       </c>
       <c r="P32" s="0">
-        <v>504.59707413473598</v>
+        <v>7588.7534318386352</v>
       </c>
       <c r="Q32" s="0">
-        <v>207.92658657882819</v>
+        <v>3171.8791676910969</v>
       </c>
       <c r="R32" s="0">
-        <v>287.19292561629368</v>
+        <v>4739.2093028971385</v>
       </c>
       <c r="S32" s="0">
-        <v>2.0342272393201455</v>
+        <v>1.6256906851264241</v>
       </c>
       <c r="T32" s="0">
-        <v>4.4763889503972862</v>
+        <v>3.1271799278324704</v>
       </c>
     </row>
     <row r="33">
@@ -2283,58 +2283,58 @@
         <v>39</v>
       </c>
       <c r="C33" s="0">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="D33" s="0">
-        <v>3955.5442352941177</v>
+        <v>929.04743749999977</v>
       </c>
       <c r="E33" s="0">
-        <v>3029.2600000000002</v>
+        <v>653.27999999999997</v>
       </c>
       <c r="F33" s="0">
-        <v>3633.209196544517</v>
+        <v>830.58048704243981</v>
       </c>
       <c r="G33" s="0">
-        <v>13200209.065855656</v>
+        <v>689863.9454556565</v>
       </c>
       <c r="H33" s="0">
-        <v>-1094.49</v>
+        <v>80.200000000000003</v>
       </c>
       <c r="I33" s="0">
-        <v>18397.919999999998</v>
+        <v>4598.1800000000003</v>
       </c>
       <c r="J33" s="0">
-        <v>1255.01</v>
+        <v>310.435</v>
       </c>
       <c r="K33" s="0">
-        <v>5424.0675000000001</v>
+        <v>1246.3499999999999</v>
       </c>
       <c r="L33" s="0">
-        <v>4169.0574999999999</v>
+        <v>935.91499999999996</v>
       </c>
       <c r="M33" s="0">
-        <v>394.07686717867705</v>
+        <v>65.663152978651979</v>
       </c>
       <c r="N33" s="0">
-        <v>0.91851057159884519</v>
+        <v>0.89401300032372133</v>
       </c>
       <c r="O33" s="0">
-        <v>322.3350387496007</v>
+        <v>98.46695045755996</v>
       </c>
       <c r="P33" s="0">
-        <v>7588.7534318386352</v>
+        <v>1759.6279245424396</v>
       </c>
       <c r="Q33" s="0">
-        <v>3171.8791676910969</v>
+        <v>799.36295904879205</v>
       </c>
       <c r="R33" s="0">
-        <v>4739.2093028971385</v>
+        <v>1058.7319159512074</v>
       </c>
       <c r="S33" s="0">
-        <v>1.6256906851264241</v>
+        <v>1.5751244538338345</v>
       </c>
       <c r="T33" s="0">
-        <v>3.1271799278324704</v>
+        <v>2.6316702643945531</v>
       </c>
     </row>
     <row r="34">
@@ -2345,58 +2345,58 @@
         <v>40</v>
       </c>
       <c r="C34" s="0">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D34" s="0">
-        <v>929.04743749999977</v>
+        <v>247.55975609756095</v>
       </c>
       <c r="E34" s="0">
-        <v>653.27999999999997</v>
+        <v>162.56999999999999</v>
       </c>
       <c r="F34" s="0">
-        <v>830.58048704243981</v>
+        <v>257.037318037175</v>
       </c>
       <c r="G34" s="0">
-        <v>689863.9454556565</v>
+        <v>66068.182863743845</v>
       </c>
       <c r="H34" s="0">
-        <v>80.200000000000003</v>
+        <v>24.920000000000002</v>
       </c>
       <c r="I34" s="0">
-        <v>4598.1800000000003</v>
+        <v>1378.8599999999999</v>
       </c>
       <c r="J34" s="0">
-        <v>310.435</v>
+        <v>79.549999999999997</v>
       </c>
       <c r="K34" s="0">
-        <v>1246.3499999999999</v>
+        <v>346.89499999999998</v>
       </c>
       <c r="L34" s="0">
-        <v>935.91499999999996</v>
+        <v>267.34499999999997</v>
       </c>
       <c r="M34" s="0">
-        <v>65.663152978651979</v>
+        <v>20.071242451811838</v>
       </c>
       <c r="N34" s="0">
-        <v>0.89401300032372133</v>
+        <v>1.0382839363271914</v>
       </c>
       <c r="O34" s="0">
-        <v>98.46695045755996</v>
+        <v>-9.4775619396140485</v>
       </c>
       <c r="P34" s="0">
-        <v>1759.6279245424396</v>
+        <v>504.59707413473598</v>
       </c>
       <c r="Q34" s="0">
-        <v>799.36295904879205</v>
+        <v>207.92658657882819</v>
       </c>
       <c r="R34" s="0">
-        <v>1058.7319159512074</v>
+        <v>287.19292561629368</v>
       </c>
       <c r="S34" s="0">
-        <v>1.5751244538338345</v>
+        <v>2.0342272393201455</v>
       </c>
       <c r="T34" s="0">
-        <v>2.6316702643945531</v>
+        <v>4.4763889503972862</v>
       </c>
     </row>
     <row r="35">
@@ -2469,58 +2469,58 @@
         <v>42</v>
       </c>
       <c r="C36" s="0">
-        <v>334</v>
+        <v>494</v>
       </c>
       <c r="D36" s="0">
-        <v>1623.1401497005991</v>
+        <v>1293.4703036437247</v>
       </c>
       <c r="E36" s="0">
-        <v>849.80500000000006</v>
+        <v>733.95000000000005</v>
       </c>
       <c r="F36" s="0">
-        <v>2398.5819008252865</v>
+        <v>1691.3618622534041</v>
       </c>
       <c r="G36" s="0">
-        <v>5753195.1349666445</v>
+        <v>2860704.9490853031</v>
       </c>
       <c r="H36" s="0">
-        <v>-6485.9099999999999</v>
+        <v>-3409.6799999999998</v>
       </c>
       <c r="I36" s="0">
-        <v>18397.919999999998</v>
+        <v>13931.299999999999</v>
       </c>
       <c r="J36" s="0">
-        <v>319.58999999999998</v>
+        <v>284.86000000000001</v>
       </c>
       <c r="K36" s="0">
-        <v>1873.3</v>
+        <v>1667.6800000000001</v>
       </c>
       <c r="L36" s="0">
-        <v>1553.71</v>
+        <v>1382.8200000000002</v>
       </c>
       <c r="M36" s="0">
-        <v>131.24456230499865</v>
+        <v>76.097967822080577</v>
       </c>
       <c r="N36" s="0">
-        <v>1.4777417102692727</v>
+        <v>1.3076155343410769</v>
       </c>
       <c r="O36" s="0">
-        <v>-775.44175112468747</v>
+        <v>-397.89155860967935</v>
       </c>
       <c r="P36" s="0">
-        <v>4021.7220505258856</v>
+        <v>2984.832165897129</v>
       </c>
       <c r="Q36" s="0">
-        <v>1364.9672066227445</v>
+        <v>1143.9539655633873</v>
       </c>
       <c r="R36" s="0">
-        <v>1881.3130927784537</v>
+        <v>1442.9866417240621</v>
       </c>
       <c r="S36" s="0">
-        <v>2.9553045352221439</v>
+        <v>2.5168598159650593</v>
       </c>
       <c r="T36" s="0">
-        <v>12.838106737892518</v>
+        <v>10.063601986863464</v>
       </c>
     </row>
     <row r="37">
@@ -2531,58 +2531,58 @@
         <v>43</v>
       </c>
       <c r="C37" s="0">
-        <v>494</v>
+        <v>334</v>
       </c>
       <c r="D37" s="0">
-        <v>1293.4703036437247</v>
+        <v>1623.1401497005991</v>
       </c>
       <c r="E37" s="0">
-        <v>733.95000000000005</v>
+        <v>849.80500000000006</v>
       </c>
       <c r="F37" s="0">
-        <v>1691.3618622534041</v>
+        <v>2398.5819008252865</v>
       </c>
       <c r="G37" s="0">
-        <v>2860704.9490853031</v>
+        <v>5753195.1349666445</v>
       </c>
       <c r="H37" s="0">
-        <v>-3409.6799999999998</v>
+        <v>-6485.9099999999999</v>
       </c>
       <c r="I37" s="0">
-        <v>13931.299999999999</v>
+        <v>18397.919999999998</v>
       </c>
       <c r="J37" s="0">
-        <v>284.86000000000001</v>
+        <v>319.58999999999998</v>
       </c>
       <c r="K37" s="0">
-        <v>1667.6800000000001</v>
+        <v>1873.3</v>
       </c>
       <c r="L37" s="0">
-        <v>1382.8200000000002</v>
+        <v>1553.71</v>
       </c>
       <c r="M37" s="0">
-        <v>76.097967822080577</v>
+        <v>131.24456230499865</v>
       </c>
       <c r="N37" s="0">
-        <v>1.3076155343410769</v>
+        <v>1.4777417102692727</v>
       </c>
       <c r="O37" s="0">
-        <v>-397.89155860967935</v>
+        <v>-775.44175112468747</v>
       </c>
       <c r="P37" s="0">
-        <v>2984.832165897129</v>
+        <v>4021.7220505258856</v>
       </c>
       <c r="Q37" s="0">
-        <v>1143.9539655633873</v>
+        <v>1364.9672066227445</v>
       </c>
       <c r="R37" s="0">
-        <v>1442.9866417240621</v>
+        <v>1881.3130927784537</v>
       </c>
       <c r="S37" s="0">
-        <v>2.5168598159650593</v>
+        <v>2.9553045352221439</v>
       </c>
       <c r="T37" s="0">
-        <v>10.063601986863464</v>
+        <v>12.838106737892518</v>
       </c>
     </row>
     <row r="38">
@@ -2593,58 +2593,58 @@
         <v>44</v>
       </c>
       <c r="C38" s="0">
-        <v>527</v>
+        <v>162</v>
       </c>
       <c r="D38" s="0">
-        <v>1268.4290132827323</v>
+        <v>2029.809135802469</v>
       </c>
       <c r="E38" s="0">
-        <v>685.40999999999997</v>
+        <v>1279.45</v>
       </c>
       <c r="F38" s="0">
-        <v>1792.128342635893</v>
+        <v>2566.9575692639978</v>
       </c>
       <c r="G38" s="0">
-        <v>3211723.9964788724</v>
+        <v>6589271.1624017321</v>
       </c>
       <c r="H38" s="0">
-        <v>-6485.9099999999999</v>
+        <v>-808.01999999999998</v>
       </c>
       <c r="I38" s="0">
-        <v>13931.299999999999</v>
+        <v>18397.919999999998</v>
       </c>
       <c r="J38" s="0">
-        <v>282.30000000000001</v>
+        <v>477.00999999999999</v>
       </c>
       <c r="K38" s="0">
-        <v>1588.52</v>
+        <v>2311.5799999999999</v>
       </c>
       <c r="L38" s="0">
-        <v>1306.22</v>
+        <v>1834.5699999999999</v>
       </c>
       <c r="M38" s="0">
-        <v>78.066336755960393</v>
+        <v>201.67923380496774</v>
       </c>
       <c r="N38" s="0">
-        <v>1.4128723987460765</v>
+        <v>1.2646300206197325</v>
       </c>
       <c r="O38" s="0">
-        <v>-523.69932935316069</v>
+        <v>-537.14843346152884</v>
       </c>
       <c r="P38" s="0">
-        <v>3060.557355918625</v>
+        <v>4596.7667050664668</v>
       </c>
       <c r="Q38" s="0">
-        <v>1115.06892622747</v>
+        <v>1631.5313529461209</v>
       </c>
       <c r="R38" s="0">
-        <v>1421.7891003379946</v>
+        <v>2428.086918658817</v>
       </c>
       <c r="S38" s="0">
-        <v>2.7516113363573584</v>
+        <v>3.0165919512504975</v>
       </c>
       <c r="T38" s="0">
-        <v>12.062425396583814</v>
+        <v>12.698888968277739</v>
       </c>
     </row>
     <row r="39">
@@ -2655,58 +2655,58 @@
         <v>45</v>
       </c>
       <c r="C39" s="0">
-        <v>269</v>
+        <v>527</v>
       </c>
       <c r="D39" s="0">
-        <v>1305.1346096654277</v>
+        <v>1268.4290132827323</v>
       </c>
       <c r="E39" s="0">
-        <v>735.61000000000001</v>
+        <v>685.40999999999997</v>
       </c>
       <c r="F39" s="0">
-        <v>1824.5188033821658</v>
+        <v>1792.128342635893</v>
       </c>
       <c r="G39" s="0">
-        <v>3328868.8638950898</v>
+        <v>3211723.9964788724</v>
       </c>
       <c r="H39" s="0">
-        <v>-3409.6799999999998</v>
+        <v>-6485.9099999999999</v>
       </c>
       <c r="I39" s="0">
-        <v>14240.790000000001</v>
+        <v>13931.299999999999</v>
       </c>
       <c r="J39" s="0">
-        <v>287.14750000000004</v>
+        <v>282.30000000000001</v>
       </c>
       <c r="K39" s="0">
-        <v>1555.7525000000001</v>
+        <v>1588.52</v>
       </c>
       <c r="L39" s="0">
-        <v>1268.605</v>
+        <v>1306.22</v>
       </c>
       <c r="M39" s="0">
-        <v>111.24287477947105</v>
+        <v>78.066336755960393</v>
       </c>
       <c r="N39" s="0">
-        <v>1.3979545020646436</v>
+        <v>1.4128723987460765</v>
       </c>
       <c r="O39" s="0">
-        <v>-519.38419371673808</v>
+        <v>-523.69932935316069</v>
       </c>
       <c r="P39" s="0">
-        <v>3129.6534130475934</v>
+        <v>3060.557355918625</v>
       </c>
       <c r="Q39" s="0">
-        <v>1086.1135001541759</v>
+        <v>1115.06892622747</v>
       </c>
       <c r="R39" s="0">
-        <v>1524.1557191766794</v>
+        <v>1421.7891003379946</v>
       </c>
       <c r="S39" s="0">
-        <v>2.8031029230490385</v>
+        <v>2.7516113363573584</v>
       </c>
       <c r="T39" s="0">
-        <v>12.512919556365528</v>
+        <v>12.062425396583814</v>
       </c>
     </row>
     <row r="40">
@@ -2717,58 +2717,58 @@
         <v>46</v>
       </c>
       <c r="C40" s="0">
-        <v>162</v>
+        <v>269</v>
       </c>
       <c r="D40" s="0">
-        <v>2029.809135802469</v>
+        <v>1305.1346096654277</v>
       </c>
       <c r="E40" s="0">
-        <v>1279.45</v>
+        <v>735.61000000000001</v>
       </c>
       <c r="F40" s="0">
-        <v>2566.9575692639978</v>
+        <v>1824.5188033821658</v>
       </c>
       <c r="G40" s="0">
-        <v>6589271.1624017321</v>
+        <v>3328868.8638950898</v>
       </c>
       <c r="H40" s="0">
-        <v>-808.01999999999998</v>
+        <v>-3409.6799999999998</v>
       </c>
       <c r="I40" s="0">
-        <v>18397.919999999998</v>
+        <v>14240.790000000001</v>
       </c>
       <c r="J40" s="0">
-        <v>477.00999999999999</v>
+        <v>287.14750000000004</v>
       </c>
       <c r="K40" s="0">
-        <v>2311.5799999999999</v>
+        <v>1555.7525000000001</v>
       </c>
       <c r="L40" s="0">
-        <v>1834.5699999999999</v>
+        <v>1268.605</v>
       </c>
       <c r="M40" s="0">
-        <v>201.67923380496774</v>
+        <v>111.24287477947105</v>
       </c>
       <c r="N40" s="0">
-        <v>1.2646300206197325</v>
+        <v>1.3979545020646436</v>
       </c>
       <c r="O40" s="0">
-        <v>-537.14843346152884</v>
+        <v>-519.38419371673808</v>
       </c>
       <c r="P40" s="0">
-        <v>4596.7667050664668</v>
+        <v>3129.6534130475934</v>
       </c>
       <c r="Q40" s="0">
-        <v>1631.5313529461209</v>
+        <v>1086.1135001541759</v>
       </c>
       <c r="R40" s="0">
-        <v>2428.086918658817</v>
+        <v>1524.1557191766794</v>
       </c>
       <c r="S40" s="0">
-        <v>3.0165919512504975</v>
+        <v>2.8031029230490385</v>
       </c>
       <c r="T40" s="0">
-        <v>12.698888968277739</v>
+        <v>12.512919556365528</v>
       </c>
     </row>
   </sheetData>
@@ -2780,8 +2780,8 @@
   <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="true"/>
-    <col min="2" max="2" width="20" customWidth="true"/>
+    <col min="1" max="1" width="15" customWidth="true"/>
+    <col min="2" max="2" width="20.85546875" customWidth="true"/>
     <col min="3" max="3" width="4.140625" customWidth="true"/>
     <col min="4" max="4" width="6.7109375" customWidth="true"/>
     <col min="5" max="5" width="11.7109375" customWidth="true"/>
@@ -2935,19 +2935,19 @@
         <v>13</v>
       </c>
       <c r="C7" s="0">
-        <v>59</v>
+        <v>291</v>
       </c>
       <c r="D7" s="0">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="E7" s="0">
-        <v>6.7796610169491522</v>
+        <v>8.2474226804123703</v>
       </c>
       <c r="F7" s="0">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G7" s="0">
-        <v>1.6949152542372881</v>
+        <v>2.7491408934707904</v>
       </c>
     </row>
     <row r="8">
@@ -2958,19 +2958,19 @@
         <v>14</v>
       </c>
       <c r="C8" s="0">
-        <v>39</v>
+        <v>119</v>
       </c>
       <c r="D8" s="0">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E8" s="0">
-        <v>12.820512820512821</v>
+        <v>6.7226890756302522</v>
       </c>
       <c r="F8" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G8" s="0">
-        <v>2.5641025641025643</v>
+        <v>3.3613445378151261</v>
       </c>
     </row>
     <row r="9">
@@ -2981,19 +2981,19 @@
         <v>15</v>
       </c>
       <c r="C9" s="0">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="D9" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E9" s="0">
-        <v>6.666666666666667</v>
+        <v>6.7796610169491522</v>
       </c>
       <c r="F9" s="0">
         <v>1</v>
       </c>
       <c r="G9" s="0">
-        <v>3.3333333333333335</v>
+        <v>1.6949152542372881</v>
       </c>
     </row>
     <row r="10">
@@ -3004,19 +3004,19 @@
         <v>16</v>
       </c>
       <c r="C10" s="0">
-        <v>291</v>
+        <v>39</v>
       </c>
       <c r="D10" s="0">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E10" s="0">
-        <v>8.2474226804123703</v>
+        <v>12.820512820512821</v>
       </c>
       <c r="F10" s="0">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G10" s="0">
-        <v>2.7491408934707904</v>
+        <v>2.5641025641025643</v>
       </c>
     </row>
     <row r="11">
@@ -3027,19 +3027,19 @@
         <v>17</v>
       </c>
       <c r="C11" s="0">
-        <v>119</v>
+        <v>30</v>
       </c>
       <c r="D11" s="0">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E11" s="0">
-        <v>6.7226890756302522</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="F11" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G11" s="0">
-        <v>3.3613445378151261</v>
+        <v>3.3333333333333335</v>
       </c>
     </row>
     <row r="12">
@@ -3050,19 +3050,19 @@
         <v>18</v>
       </c>
       <c r="C12" s="0">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D12" s="0">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E12" s="0">
-        <v>9.5999999999999997</v>
+        <v>6.7226890756302522</v>
       </c>
       <c r="F12" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G12" s="0">
-        <v>1.6000000000000001</v>
+        <v>3.3613445378151261</v>
       </c>
     </row>
     <row r="13">
@@ -3073,19 +3073,19 @@
         <v>19</v>
       </c>
       <c r="C13" s="0">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="D13" s="0">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E13" s="0">
-        <v>6.7226890756302522</v>
+        <v>14.492753623188406</v>
       </c>
       <c r="F13" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G13" s="0">
-        <v>3.3613445378151261</v>
+        <v>2.8985507246376812</v>
       </c>
     </row>
     <row r="14">
@@ -3096,19 +3096,19 @@
         <v>20</v>
       </c>
       <c r="C14" s="0">
-        <v>46</v>
+        <v>221</v>
       </c>
       <c r="D14" s="0">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E14" s="0">
-        <v>10.869565217391305</v>
+        <v>7.6923076923076925</v>
       </c>
       <c r="F14" s="0">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G14" s="0">
-        <v>2.1739130434782608</v>
+        <v>2.7149321266968327</v>
       </c>
     </row>
     <row r="15">
@@ -3119,19 +3119,19 @@
         <v>21</v>
       </c>
       <c r="C15" s="0">
-        <v>69</v>
+        <v>378</v>
       </c>
       <c r="D15" s="0">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E15" s="0">
-        <v>14.492753623188406</v>
+        <v>8.4656084656084651</v>
       </c>
       <c r="F15" s="0">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G15" s="0">
-        <v>2.8985507246376812</v>
+        <v>2.3809523809523809</v>
       </c>
     </row>
     <row r="16">
@@ -3142,19 +3142,19 @@
         <v>22</v>
       </c>
       <c r="C16" s="0">
-        <v>378</v>
+        <v>125</v>
       </c>
       <c r="D16" s="0">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E16" s="0">
-        <v>8.4656084656084651</v>
+        <v>9.5999999999999997</v>
       </c>
       <c r="F16" s="0">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G16" s="0">
-        <v>2.3809523809523809</v>
+        <v>1.6000000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -3165,19 +3165,19 @@
         <v>23</v>
       </c>
       <c r="C17" s="0">
-        <v>221</v>
+        <v>46</v>
       </c>
       <c r="D17" s="0">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E17" s="0">
-        <v>7.6923076923076925</v>
+        <v>10.869565217391305</v>
       </c>
       <c r="F17" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G17" s="0">
-        <v>2.7149321266968327</v>
+        <v>2.1739130434782608</v>
       </c>
     </row>
     <row r="18">
@@ -3510,19 +3510,19 @@
         <v>38</v>
       </c>
       <c r="C32" s="0">
-        <v>164</v>
+        <v>85</v>
       </c>
       <c r="D32" s="0">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E32" s="0">
-        <v>6.7073170731707315</v>
+        <v>4.7058823529411766</v>
       </c>
       <c r="F32" s="0">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G32" s="0">
-        <v>2.4390243902439024</v>
+        <v>1.1764705882352942</v>
       </c>
     </row>
     <row r="33">
@@ -3533,19 +3533,19 @@
         <v>39</v>
       </c>
       <c r="C33" s="0">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="D33" s="0">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E33" s="0">
-        <v>4.7058823529411766</v>
+        <v>4.375</v>
       </c>
       <c r="F33" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="0">
-        <v>1.1764705882352942</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="34">
@@ -3556,19 +3556,19 @@
         <v>40</v>
       </c>
       <c r="C34" s="0">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="D34" s="0">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E34" s="0">
-        <v>4.375</v>
+        <v>6.7073170731707315</v>
       </c>
       <c r="F34" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G34" s="0">
-        <v>1.25</v>
+        <v>2.4390243902439024</v>
       </c>
     </row>
     <row r="35">
@@ -3602,19 +3602,19 @@
         <v>42</v>
       </c>
       <c r="C36" s="0">
-        <v>334</v>
+        <v>494</v>
       </c>
       <c r="D36" s="0">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E36" s="0">
-        <v>10.479041916167665</v>
+        <v>8.5020242914979764</v>
       </c>
       <c r="F36" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G36" s="0">
-        <v>3.2934131736526946</v>
+        <v>2.0242914979757085</v>
       </c>
     </row>
     <row r="37">
@@ -3625,19 +3625,19 @@
         <v>43</v>
       </c>
       <c r="C37" s="0">
-        <v>494</v>
+        <v>334</v>
       </c>
       <c r="D37" s="0">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E37" s="0">
-        <v>8.5020242914979764</v>
+        <v>10.479041916167665</v>
       </c>
       <c r="F37" s="0">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G37" s="0">
-        <v>2.0242914979757085</v>
+        <v>3.2934131736526946</v>
       </c>
     </row>
     <row r="38">
@@ -3648,19 +3648,19 @@
         <v>44</v>
       </c>
       <c r="C38" s="0">
-        <v>527</v>
+        <v>162</v>
       </c>
       <c r="D38" s="0">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="E38" s="0">
-        <v>8.5388994307400381</v>
+        <v>11.111111111111111</v>
       </c>
       <c r="F38" s="0">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G38" s="0">
-        <v>2.0872865275142316</v>
+        <v>1.8518518518518519</v>
       </c>
     </row>
     <row r="39">
@@ -3671,19 +3671,19 @@
         <v>45</v>
       </c>
       <c r="C39" s="0">
-        <v>269</v>
+        <v>527</v>
       </c>
       <c r="D39" s="0">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E39" s="0">
-        <v>10.408921933085502</v>
+        <v>8.5388994307400381</v>
       </c>
       <c r="F39" s="0">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G39" s="0">
-        <v>2.2304832713754648</v>
+        <v>2.0872865275142316</v>
       </c>
     </row>
     <row r="40">
@@ -3694,19 +3694,19 @@
         <v>46</v>
       </c>
       <c r="C40" s="0">
-        <v>162</v>
+        <v>269</v>
       </c>
       <c r="D40" s="0">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="E40" s="0">
-        <v>11.111111111111111</v>
+        <v>10.408921933085502</v>
       </c>
       <c r="F40" s="0">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G40" s="0">
-        <v>1.8518518518518519</v>
+        <v>2.2304832713754648</v>
       </c>
     </row>
   </sheetData>
